--- a/Excel/10. Vlookup_&_Xlookup/Lecture_5_Lookups.xlsx
+++ b/Excel/10. Vlookup_&_Xlookup/Lecture_5_Lookups.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ds_30\Excel\Data files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Weekend\Excel\10. Vlookup_&amp;_Xlookup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E188E3E9-ED63-4121-9C25-615B7D2C153E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEC1903-B2C1-4F6F-92D7-2639C277207F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="862" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="862" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VLOOKUP" sheetId="2" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="43">
   <si>
     <t>Example</t>
   </si>
@@ -1526,23 +1526,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA21"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="0.7265625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="3.7265625" style="17" customWidth="1"/>
-    <col min="11" max="11" width="3.7265625" customWidth="1"/>
-    <col min="12" max="16" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="0.77734375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="3.77734375" style="17" customWidth="1"/>
+    <col min="11" max="11" width="3.77734375" customWidth="1"/>
+    <col min="12" max="16" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -1575,11 +1575,11 @@
       <c r="Z1" s="41"/>
       <c r="AA1" s="15"/>
     </row>
-    <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="12"/>
     </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
       <c r="C4" s="42" t="s">
         <v>12</v>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="45"/>
       <c r="D5" s="46"/>
@@ -1636,7 +1636,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="45"/>
       <c r="D6" s="46"/>
       <c r="E6" s="46"/>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="P6" s="22"/>
     </row>
-    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="45"/>
       <c r="D7" s="46"/>
       <c r="E7" s="46"/>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="P7" s="22"/>
     </row>
-    <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="45"/>
       <c r="D8" s="46"/>
       <c r="E8" s="46"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P8" s="22"/>
     </row>
-    <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="45"/>
       <c r="D9" s="46"/>
       <c r="E9" s="46"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P9" s="22"/>
     </row>
-    <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="45"/>
       <c r="D10" s="46"/>
       <c r="E10" s="46"/>
@@ -1724,7 +1724,7 @@
       <c r="G10" s="47"/>
       <c r="M10" s="21"/>
     </row>
-    <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
       <c r="C11" s="48"/>
       <c r="D11" s="49"/>
@@ -1734,12 +1734,12 @@
       <c r="M11" s="21"/>
       <c r="O11" s="25"/>
     </row>
-    <row r="12" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B12" s="4"/>
       <c r="C12" s="12"/>
       <c r="M12" s="21"/>
     </row>
-    <row r="13" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C13" s="13"/>
       <c r="L13" s="27" t="s">
         <v>1</v>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="N13" s="29"/>
     </row>
-    <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="51" t="s">
         <v>31</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="54"/>
       <c r="D15" s="55"/>
       <c r="E15" s="55"/>
@@ -1777,7 +1777,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="54"/>
       <c r="D16" s="55"/>
       <c r="E16" s="55"/>
@@ -1790,7 +1790,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5"/>
       <c r="C17" s="54"/>
       <c r="D17" s="55"/>
@@ -1804,7 +1804,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6"/>
       <c r="C18" s="54"/>
       <c r="D18" s="55"/>
@@ -1818,7 +1818,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="6"/>
       <c r="C19" s="54"/>
       <c r="D19" s="55"/>
@@ -1832,7 +1832,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="54"/>
       <c r="D20" s="55"/>
       <c r="E20" s="55"/>
@@ -1845,7 +1845,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C21" s="57"/>
       <c r="D21" s="58"/>
       <c r="E21" s="58"/>
@@ -1878,23 +1878,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AA21"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="0.7265625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="3.7265625" style="17" customWidth="1"/>
-    <col min="11" max="11" width="3.7265625" customWidth="1"/>
-    <col min="12" max="22" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="0.77734375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="3.77734375" style="17" customWidth="1"/>
+    <col min="11" max="11" width="3.77734375" customWidth="1"/>
+    <col min="12" max="22" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>33</v>
@@ -1927,11 +1927,11 @@
       <c r="Z1" s="41"/>
       <c r="AA1" s="15"/>
     </row>
-    <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="12"/>
     </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
       <c r="C4" s="42" t="s">
         <v>30</v>
@@ -1946,7 +1946,7 @@
       <c r="K4" s="7"/>
       <c r="M4" s="26"/>
     </row>
-    <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="45"/>
       <c r="D5" s="46"/>
@@ -1970,7 +1970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="45"/>
       <c r="D6" s="46"/>
       <c r="E6" s="46"/>
@@ -1989,7 +1989,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="45"/>
       <c r="D7" s="46"/>
       <c r="E7" s="46"/>
@@ -2008,7 +2008,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="45"/>
       <c r="D8" s="46"/>
       <c r="E8" s="46"/>
@@ -2027,7 +2027,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="45"/>
       <c r="D9" s="46"/>
       <c r="E9" s="46"/>
@@ -2046,7 +2046,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="45"/>
       <c r="D10" s="46"/>
       <c r="E10" s="46"/>
@@ -2065,7 +2065,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
       <c r="C11" s="48"/>
       <c r="D11" s="49"/>
@@ -2076,22 +2076,42 @@
         <v>16</v>
       </c>
       <c r="M11" s="23">
-        <f>HLOOKUP(M5,$M$15:$S$17,2,0)</f>
+        <f>HLOOKUP(M5,$M$15:$S$16,2,0)</f>
         <v>83</v>
       </c>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-    </row>
-    <row r="12" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="N11" s="23">
+        <f t="shared" ref="N11:O11" si="0">HLOOKUP(N5,$M$15:$S$16,2,0)</f>
+        <v>99</v>
+      </c>
+      <c r="O11" s="23">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B12" s="4"/>
       <c r="C12" s="12"/>
-      <c r="M12" s="21"/>
-    </row>
-    <row r="13" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="L12" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="23">
+        <f>HLOOKUP(M5,$M$15:$S$17,3,0)</f>
+        <v>53</v>
+      </c>
+      <c r="N12" s="23">
+        <f t="shared" ref="N12:O12" si="1">HLOOKUP(N5,$M$15:$S$17,3,0)</f>
+        <v>65</v>
+      </c>
+      <c r="O12" s="23">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C13" s="13"/>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
       <c r="C14" s="51" t="s">
         <v>32</v>
@@ -2102,7 +2122,7 @@
       <c r="G14" s="53"/>
       <c r="M14" s="21"/>
     </row>
-    <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
       <c r="C15" s="54"/>
       <c r="D15" s="55"/>
@@ -2134,7 +2154,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
       <c r="C16" s="54"/>
       <c r="D16" s="55"/>
@@ -2166,7 +2186,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="54"/>
       <c r="D17" s="55"/>
       <c r="E17" s="55"/>
@@ -2197,28 +2217,28 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="54"/>
       <c r="D18" s="55"/>
       <c r="E18" s="55"/>
       <c r="F18" s="55"/>
       <c r="G18" s="56"/>
     </row>
-    <row r="19" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="54"/>
       <c r="D19" s="55"/>
       <c r="E19" s="55"/>
       <c r="F19" s="55"/>
       <c r="G19" s="56"/>
     </row>
-    <row r="20" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="54"/>
       <c r="D20" s="55"/>
       <c r="E20" s="55"/>
       <c r="F20" s="55"/>
       <c r="G20" s="56"/>
     </row>
-    <row r="21" spans="3:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C21" s="57"/>
       <c r="D21" s="58"/>
       <c r="E21" s="58"/>
@@ -2245,23 +2265,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z24"/>
-  <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" customWidth="1"/>
-    <col min="8" max="8" width="7.1796875" customWidth="1"/>
-    <col min="9" max="9" width="0.7265625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="3.7265625" style="17" customWidth="1"/>
-    <col min="11" max="11" width="3.7265625" customWidth="1"/>
-    <col min="12" max="12" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="7.21875" customWidth="1"/>
+    <col min="9" max="9" width="0.77734375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="3.77734375" style="17" customWidth="1"/>
+    <col min="11" max="11" width="3.77734375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -2293,8 +2313,8 @@
       <c r="Y1" s="41"/>
       <c r="Z1" s="15"/>
     </row>
-    <row r="2" spans="1:26" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:26" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="12"/>
       <c r="M3">
         <v>1</v>
@@ -2306,7 +2326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
       <c r="C4" s="60" t="s">
         <v>34</v>
@@ -2332,7 +2352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="63"/>
       <c r="D5" s="64"/>
@@ -2356,7 +2376,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="63"/>
       <c r="D6" s="64"/>
       <c r="E6" s="64"/>
@@ -2375,7 +2395,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="63"/>
       <c r="D7" s="64"/>
       <c r="E7" s="64"/>
@@ -2394,7 +2414,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="63"/>
       <c r="D8" s="64"/>
       <c r="E8" s="64"/>
@@ -2413,7 +2433,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="63"/>
       <c r="D9" s="64"/>
       <c r="E9" s="64"/>
@@ -2432,21 +2452,21 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="63"/>
       <c r="D10" s="64"/>
       <c r="E10" s="64"/>
       <c r="F10" s="64"/>
       <c r="G10" s="65"/>
     </row>
-    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="63"/>
       <c r="D11" s="64"/>
       <c r="E11" s="64"/>
       <c r="F11" s="64"/>
       <c r="G11" s="65"/>
     </row>
-    <row r="12" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C12" s="63"/>
       <c r="D12" s="64"/>
       <c r="E12" s="64"/>
@@ -2456,11 +2476,11 @@
         <v>22</v>
       </c>
       <c r="M12" s="22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N12" s="23"/>
     </row>
-    <row r="13" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C13" s="63"/>
       <c r="D13" s="64"/>
       <c r="E13" s="64"/>
@@ -2470,14 +2490,14 @@
         <v>23</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N13" s="23">
         <f>IF(M13="Maths",1,IF(M13="Science",2,3))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="5"/>
       <c r="C14" s="66"/>
       <c r="D14" s="67"/>
@@ -2489,25 +2509,21 @@
       </c>
       <c r="M14" s="23">
         <f>INDEX(M5:O9,M12,N13)</f>
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="N14" s="23"/>
     </row>
-    <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B15" s="4"/>
       <c r="C15" s="12"/>
-      <c r="M15" cm="1">
-        <f t="array" ref="M15">INDEX($M$5:$O$9,M12,N13)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="16" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C16" s="13"/>
       <c r="L16" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5"/>
       <c r="C17" s="51" t="s">
         <v>35</v>
@@ -2517,15 +2533,19 @@
       <c r="F17" s="52"/>
       <c r="G17" s="53"/>
     </row>
-    <row r="18" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6"/>
       <c r="C18" s="54"/>
       <c r="D18" s="55"/>
       <c r="E18" s="55"/>
       <c r="F18" s="55"/>
       <c r="G18" s="56"/>
-    </row>
-    <row r="19" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M18" cm="1">
+        <f t="array" ref="M18">INDEX($M$5:$O$9,M12,N13)</f>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="6"/>
       <c r="C19" s="54"/>
       <c r="D19" s="55"/>
@@ -2533,35 +2553,35 @@
       <c r="F19" s="55"/>
       <c r="G19" s="56"/>
     </row>
-    <row r="20" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="54"/>
       <c r="D20" s="55"/>
       <c r="E20" s="55"/>
       <c r="F20" s="55"/>
       <c r="G20" s="56"/>
     </row>
-    <row r="21" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="54"/>
       <c r="D21" s="55"/>
       <c r="E21" s="55"/>
       <c r="F21" s="55"/>
       <c r="G21" s="56"/>
     </row>
-    <row r="22" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="54"/>
       <c r="D22" s="55"/>
       <c r="E22" s="55"/>
       <c r="F22" s="55"/>
       <c r="G22" s="56"/>
     </row>
-    <row r="23" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="54"/>
       <c r="D23" s="55"/>
       <c r="E23" s="55"/>
       <c r="F23" s="55"/>
       <c r="G23" s="56"/>
     </row>
-    <row r="24" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C24" s="57"/>
       <c r="D24" s="58"/>
       <c r="E24" s="58"/>
@@ -2588,24 +2608,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Z23"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="0.7265625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="3.7265625" style="17" customWidth="1"/>
-    <col min="11" max="11" width="3.7265625" customWidth="1"/>
-    <col min="12" max="12" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="15.7265625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="0.77734375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="3.77734375" style="17" customWidth="1"/>
+    <col min="11" max="11" width="3.77734375" customWidth="1"/>
+    <col min="12" max="12" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>41</v>
@@ -2637,8 +2657,8 @@
       <c r="Y1" s="41"/>
       <c r="Z1" s="15"/>
     </row>
-    <row r="2" spans="1:26" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:26" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="12"/>
       <c r="M3" s="36">
         <v>1</v>
@@ -2650,7 +2670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
       <c r="C4" s="60" t="s">
         <v>36</v>
@@ -2679,7 +2699,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="63"/>
       <c r="D5" s="64"/>
@@ -2709,7 +2729,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="63"/>
       <c r="D6" s="64"/>
       <c r="E6" s="64"/>
@@ -2735,7 +2755,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="63"/>
       <c r="D7" s="64"/>
       <c r="E7" s="64"/>
@@ -2761,7 +2781,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="63"/>
       <c r="D8" s="64"/>
       <c r="E8" s="64"/>
@@ -2787,7 +2807,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="63"/>
       <c r="D9" s="64"/>
       <c r="E9" s="64"/>
@@ -2813,7 +2833,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="5"/>
       <c r="C10" s="66"/>
       <c r="D10" s="67"/>
@@ -2836,14 +2856,14 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B11" s="4"/>
       <c r="C11" s="12"/>
     </row>
-    <row r="12" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C12" s="13"/>
     </row>
-    <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
       <c r="C13" s="51" t="s">
         <v>37</v>
@@ -2856,7 +2876,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6"/>
       <c r="C14" s="54"/>
       <c r="D14" s="55"/>
@@ -2864,7 +2884,7 @@
       <c r="F14" s="55"/>
       <c r="G14" s="56"/>
     </row>
-    <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
       <c r="C15" s="54"/>
       <c r="D15" s="55"/>
@@ -2882,7 +2902,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="54"/>
       <c r="D16" s="55"/>
       <c r="E16" s="55"/>
@@ -2898,14 +2918,14 @@
       <c r="N16" s="23"/>
       <c r="O16" s="23"/>
     </row>
-    <row r="17" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="54"/>
       <c r="D17" s="55"/>
       <c r="E17" s="55"/>
       <c r="F17" s="55"/>
       <c r="G17" s="56"/>
     </row>
-    <row r="18" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="54"/>
       <c r="D18" s="55"/>
       <c r="E18" s="55"/>
@@ -2915,14 +2935,14 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="54"/>
       <c r="D19" s="55"/>
       <c r="E19" s="55"/>
       <c r="F19" s="55"/>
       <c r="G19" s="56"/>
     </row>
-    <row r="20" spans="3:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C20" s="57"/>
       <c r="D20" s="58"/>
       <c r="E20" s="58"/>
@@ -2933,7 +2953,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L21" s="22" t="s">
         <v>5</v>
       </c>
@@ -2946,13 +2966,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L22" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="M22" s="23"/>
-    </row>
-    <row r="23" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M22" s="23">
+        <f>MATCH(P6,M6:O6,0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L23" s="22" t="s">
         <v>7</v>
       </c>
@@ -2978,24 +3001,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Z21"/>
-  <sheetFormatPr defaultColWidth="13.7265625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.77734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="0.7265625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="3.7265625" style="17" customWidth="1"/>
-    <col min="11" max="11" width="3.7265625" customWidth="1"/>
-    <col min="12" max="12" width="17.81640625" style="37" customWidth="1"/>
-    <col min="13" max="16384" width="13.7265625" style="37"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="0.77734375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="3.77734375" style="17" customWidth="1"/>
+    <col min="11" max="11" width="3.77734375" customWidth="1"/>
+    <col min="12" max="12" width="17.77734375" style="37" customWidth="1"/>
+    <col min="13" max="16384" width="13.77734375" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" customFormat="1" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" customFormat="1" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>40</v>
@@ -3027,16 +3050,16 @@
       <c r="Y1" s="41"/>
       <c r="Z1" s="15"/>
     </row>
-    <row r="2" spans="1:26" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="I2" s="9"/>
       <c r="J2" s="17"/>
     </row>
-    <row r="3" spans="1:26" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:26" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="12"/>
       <c r="I3" s="9"/>
       <c r="J3" s="17"/>
     </row>
-    <row r="4" spans="1:26" ht="21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="21" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
       <c r="C4" s="60" t="s">
         <v>38</v>
@@ -3065,7 +3088,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="63"/>
       <c r="D5" s="64"/>
@@ -3093,7 +3116,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C6" s="63"/>
       <c r="D6" s="64"/>
       <c r="E6" s="64"/>
@@ -3113,7 +3136,7 @@
       </c>
       <c r="P6" s="24"/>
     </row>
-    <row r="7" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C7" s="63"/>
       <c r="D7" s="64"/>
       <c r="E7" s="64"/>
@@ -3133,7 +3156,7 @@
       </c>
       <c r="P7" s="24"/>
     </row>
-    <row r="8" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C8" s="63"/>
       <c r="D8" s="64"/>
       <c r="E8" s="64"/>
@@ -3153,7 +3176,7 @@
       </c>
       <c r="P8" s="24"/>
     </row>
-    <row r="9" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C9" s="63"/>
       <c r="D9" s="64"/>
       <c r="E9" s="64"/>
@@ -3173,7 +3196,7 @@
       </c>
       <c r="P9" s="24"/>
     </row>
-    <row r="10" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="5"/>
       <c r="C10" s="66"/>
       <c r="D10" s="67"/>
@@ -3182,17 +3205,17 @@
       <c r="G10" s="68"/>
       <c r="M10" s="38"/>
     </row>
-    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B11" s="4"/>
       <c r="C11" s="12"/>
       <c r="M11" s="38"/>
       <c r="O11" s="39"/>
     </row>
-    <row r="12" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C12" s="13"/>
       <c r="M12" s="38"/>
     </row>
-    <row r="13" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
       <c r="C13" s="51" t="s">
         <v>39</v>
@@ -3208,7 +3231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" s="6"/>
       <c r="C14" s="54"/>
       <c r="D14" s="55"/>
@@ -3222,7 +3245,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
       <c r="C15" s="54"/>
       <c r="D15" s="55"/>
@@ -3236,7 +3259,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C16" s="54"/>
       <c r="D16" s="55"/>
       <c r="E16" s="55"/>
@@ -3249,7 +3272,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="3:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C17" s="54"/>
       <c r="D17" s="55"/>
       <c r="E17" s="55"/>
@@ -3262,7 +3285,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="3:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C18" s="54"/>
       <c r="D18" s="55"/>
       <c r="E18" s="55"/>
@@ -3275,7 +3298,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="3:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C19" s="54"/>
       <c r="D19" s="55"/>
       <c r="E19" s="55"/>
@@ -3288,7 +3311,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="3:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C20" s="57"/>
       <c r="D20" s="58"/>
       <c r="E20" s="58"/>
@@ -3301,7 +3324,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="3:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="M21" s="24">
         <v>45</v>
       </c>
